--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>917.8</v>
+        <v>894.36</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>338.53</v>
+        <v>329.89</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3074.47</v>
+        <v>2995.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3970.97</v>
+        <v>3869.57</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>74902.45</v>
+        <v>72989.75999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>31542.73</v>
+        <v>30737.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10231.17</v>
+        <v>9969.91</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65159.2</v>
+        <v>63495.31</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>16968.39</v>
+        <v>16535.09</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>112.96</v>
+        <v>110.08</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>33360.09</v>
+        <v>32709.41</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>29414.6</v>
+        <v>28840.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7141.48</v>
+        <v>7002.19</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2262.53</v>
+        <v>2218.4</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>236.43</v>
+        <v>231.82</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7673.37</v>
+        <v>7493.87</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14469.04</v>
+        <v>14130.56</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>80602.67</v>
+        <v>78717.10000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1131.27</v>
+        <v>1104.8</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31677.12</v>
+        <v>30936.08</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>30091.67</v>
+        <v>29387.72</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6234.24</v>
+        <v>6088.4</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>52354.12</v>
+        <v>51603.72</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8920.41</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>49893.06</v>
+        <v>49177.93</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>70543.89</v>
+        <v>69532.77</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6454.18</v>
+        <v>6361.67</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>543.01</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>16625.65</v>
+        <v>16387.35</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>13010.21</v>
+        <v>12823.73</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>14648.19</v>
+        <v>14462.26</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>683.51</v>
+        <v>674.84</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>412.69</v>
+        <v>407.45</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11193.03</v>
+        <v>11050.95</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8549.26</v>
+        <v>8440.74</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>547.02</v>
+        <v>540.08</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>800.65</v>
+        <v>790.49</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1564.23</v>
+        <v>1544.37</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>261145.19</v>
+        <v>257830.51</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21853.75</v>
+        <v>21576.36</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22035.7</v>
+        <v>21718.16</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16120.53</v>
+        <v>15888.24</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>15778.78</v>
+        <v>15551.41</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>26491.41</v>
+        <v>26109.67</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8825.99</v>
+        <v>8698.809999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>11042.74</v>
+        <v>10883.61</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7890.58</v>
+        <v>7776.87</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>24551.57</v>
+        <v>24197.78</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>30054.05</v>
+        <v>29620.97</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9801.280000000001</v>
+        <v>9660.049999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9896.219999999999</v>
+        <v>9753.610000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2758.93</v>
+        <v>2719.18</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>192.37</v>
+        <v>189.6</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9591.719999999999</v>
+        <v>9467.75</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1278.78</v>
+        <v>1262.26</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7679.82</v>
+        <v>7580.57</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>72542.41</v>
+        <v>71604.84</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>15260.77</v>
+        <v>15063.54</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2837.21</v>
+        <v>2800.54</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>33811.34</v>
+        <v>33374.35</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3655.96</v>
+        <v>3608.71</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14706.45</v>
+        <v>14516.38</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>368.09</v>
+        <v>363.33</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>47751.71</v>
+        <v>47134.55</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>20389.25</v>
+        <v>20349.1</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>43994.01</v>
+        <v>43907.37</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>48490.57</v>
+        <v>48395.07</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>70298.42999999999</v>
+        <v>70159.98</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>644.8200000000001</v>
+        <v>643.55</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>43310.51</v>
+        <v>43225.21</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>52466.63</v>
+        <v>52363.31</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11837.46</v>
+        <v>11814.15</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>12081.92</v>
+        <v>12081.99</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8776.02</v>
+        <v>8776.08</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>67875.94</v>
+        <v>67876.38</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25114.1</v>
+        <v>25114.26</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2384.6</v>
+        <v>2384.62</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10164.75</v>
+        <v>10164.81</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23659.57</v>
+        <v>23659.72</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10939.36</v>
+        <v>10939.43</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>6649.72</v>
+        <v>6649.76</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10252.66</v>
+        <v>10266.9</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>39594.3</v>
+        <v>39649.27</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7646.51</v>
+        <v>7657.12</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>19302.84</v>
+        <v>19329.64</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>112.96</v>
+        <v>113.12</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>37958.49</v>
+        <v>38011.19</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>9615.76</v>
+        <v>9629.110000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>12810.45</v>
+        <v>12828.24</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>12443.92</v>
+        <v>12461.2</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1357.52</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2263.45</v>
+        <v>2266.59</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11510.06</v>
+        <v>11502.2</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2983.72</v>
+        <v>2981.68</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5550.29</v>
+        <v>5546.5</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3572.85</v>
+        <v>3570.41</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1450.42</v>
+        <v>1449.43</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>11902.33</v>
+        <v>11894.2</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>9371.4</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8997.52</v>
+        <v>8991.370000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1128.44</v>
+        <v>1127.67</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>51844.19</v>
+        <v>51666.26</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>52630.49</v>
+        <v>52449.85</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>176.79</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>20362.78</v>
+        <v>20292.89</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>8291.33</v>
+        <v>8262.870000000001</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6577.63</v>
+        <v>6542.88</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3750.71</v>
+        <v>3730.9</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>15984.78</v>
+        <v>15900.34</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5571.9</v>
+        <v>5542.47</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>77283.37</v>
+        <v>76875.12</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>12182.83</v>
+        <v>12118.47</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10317.14</v>
+        <v>10262.64</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>358.43</v>
+        <v>356.54</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2827.64</v>
+        <v>2812.7</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4841.82</v>
+        <v>4816.24</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1131.82</v>
+        <v>1125.84</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>31372.75</v>
+        <v>31176.16</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4745.33</v>
+        <v>4715.59</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>21403.55</v>
+        <v>21269.42</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>30100.8</v>
+        <v>29912.17</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>13637.97</v>
+        <v>13552.51</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4443.01</v>
+        <v>4415.16</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2813.57</v>
+        <v>2795.94</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5092.56</v>
+        <v>5060.65</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>22568.75</v>
+        <v>22427.32</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>14144.59</v>
+        <v>14055.95</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>859.76</v>
+        <v>865.4</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3393.68</v>
+        <v>3415.92</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>56563.28</v>
+        <v>56933.99</v>
       </c>
     </row>
     <row r="133">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>126814.88</v>
+        <v>127646.01</v>
       </c>
     </row>
     <row r="134">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3620.05</v>
+        <v>3643.78</v>
       </c>
     </row>
     <row r="135">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>14161.89</v>
+        <v>14254.71</v>
       </c>
     </row>
     <row r="136">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1244.39</v>
+        <v>1252.55</v>
       </c>
     </row>
     <row r="137">
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>767.34</v>
+        <v>772.37</v>
       </c>
     </row>
     <row r="138">
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="139">
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6650.26</v>
+        <v>6739.81</v>
       </c>
     </row>
     <row r="140">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16821.96</v>
+        <v>17048.49</v>
       </c>
     </row>
     <row r="141">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>36200.5</v>
+        <v>36687.99</v>
       </c>
     </row>
     <row r="142">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>268.68</v>
+        <v>272.29</v>
       </c>
     </row>
     <row r="143">
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>11312.66</v>
+        <v>11465</v>
       </c>
     </row>
     <row r="144">
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>19108.21</v>
+        <v>19365.53</v>
       </c>
     </row>
     <row r="145">
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5115.58</v>
+        <v>5184.47</v>
       </c>
     </row>
     <row r="146">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>45137.5</v>
+        <v>45824.67</v>
       </c>
     </row>
     <row r="147">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>15837.85</v>
+        <v>16078.96</v>
       </c>
     </row>
     <row r="148">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>43265.37</v>
+        <v>43924.04</v>
       </c>
     </row>
     <row r="149">
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>16968.39</v>
+        <v>17226.72</v>
       </c>
     </row>
     <row r="150">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1087.06</v>
+        <v>1103.61</v>
       </c>
     </row>
     <row r="151">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>39147.11</v>
+        <v>39743.08</v>
       </c>
     </row>
     <row r="152">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>26570.26</v>
+        <v>26974.77</v>
       </c>
     </row>
     <row r="153">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>10940.7</v>
+        <v>11107.26</v>
       </c>
     </row>
     <row r="154">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1182.17</v>
+        <v>1200.17</v>
       </c>
     </row>
     <row r="155">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>6787.59</v>
+        <v>6890.93</v>
       </c>
     </row>
     <row r="156">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>18173.22</v>
+        <v>18449.89</v>
       </c>
     </row>
     <row r="157">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>13971.13</v>
+        <v>14183.82</v>
       </c>
     </row>
     <row r="158">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>65148.32</v>
+        <v>66140.14</v>
       </c>
     </row>
     <row r="159">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>24887.84</v>
+        <v>25266.74</v>
       </c>
     </row>
     <row r="160">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>40932.27</v>
+        <v>41555.42</v>
       </c>
     </row>
     <row r="161">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>28281.64</v>
+        <v>28712.2</v>
       </c>
     </row>
     <row r="162">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>43549.09</v>
+        <v>44212.08</v>
       </c>
     </row>
     <row r="163">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>678.76</v>
+        <v>695.27</v>
       </c>
     </row>
     <row r="164">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>22729.95</v>
+        <v>23282.69</v>
       </c>
     </row>
     <row r="165">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>9856.1</v>
+        <v>10095.77</v>
       </c>
     </row>
     <row r="166">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>8766.35</v>
+        <v>8979.52</v>
       </c>
     </row>
     <row r="167">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1550.8</v>
+        <v>1588.51</v>
       </c>
     </row>
     <row r="168">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5587.38</v>
+        <v>5723.25</v>
       </c>
     </row>
     <row r="169">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>569.59</v>
+        <v>583.4400000000001</v>
       </c>
     </row>
     <row r="170">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6639.08</v>
+        <v>6800.53</v>
       </c>
     </row>
     <row r="171">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>12829.88</v>
+        <v>13141.88</v>
       </c>
     </row>
     <row r="172">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>8939.91</v>
+        <v>9157.309999999999</v>
       </c>
     </row>
     <row r="173">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>26019.11</v>
+        <v>26651.84</v>
       </c>
     </row>
     <row r="174">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1455.15</v>
+        <v>1490.53</v>
       </c>
     </row>
     <row r="175">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>36529.3</v>
+        <v>37417.61</v>
       </c>
     </row>
     <row r="176">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>13575.19</v>
+        <v>13905.31</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3836.69</v>
+        <v>3929.99</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>389.16</v>
+        <v>398.62</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>149.89</v>
+        <v>153.54</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>36990.18</v>
+        <v>37889.7</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>24420.15</v>
+        <v>25013.99</v>
       </c>
     </row>
     <row r="182">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2262.52</v>
+        <v>2317.54</v>
       </c>
     </row>
     <row r="183">
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1149.93</v>
+        <v>1177.9</v>
       </c>
     </row>
     <row r="184">
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7234.9</v>
+        <v>7410.83</v>
       </c>
     </row>
     <row r="185">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5696.22</v>
+        <v>5834.74</v>
       </c>
     </row>
     <row r="186">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>28768.5</v>
+        <v>29495.77</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5373.51</v>
+        <v>5509.35</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3325.13</v>
+        <v>3409.19</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>41629.67</v>
+        <v>42682.07</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>45785.81</v>
+        <v>46943.28</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2828.16</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>9050.129999999999</v>
+        <v>9278.91</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>59108.63</v>
+        <v>60602.9</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>9229.43</v>
+        <v>9509.299999999999</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>23220.81</v>
+        <v>23924.94</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>31972.39</v>
+        <v>32941.9</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>58561.07</v>
+        <v>60336.82</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>80602.67</v>
+        <v>83046.8</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>32241.07</v>
+        <v>33218.72</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>440.63</v>
+        <v>453.99</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>16968.99</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>27182.34</v>
+        <v>28006.59</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8952.27</v>
+        <v>9223.73</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>15200.97</v>
+        <v>15661.91</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>10103.28</v>
+        <v>10409.64</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>662.47</v>
+        <v>682.5599999999999</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2262.25</v>
+        <v>2330.85</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>271.5</v>
+        <v>279.74</v>
       </c>
     </row>
     <row r="209">
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>202498.04</v>
+        <v>208638.41</v>
       </c>
     </row>
     <row r="210">
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>33097.18</v>
+        <v>34100.79</v>
       </c>
     </row>
     <row r="211">
@@ -13334,7 +13334,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>44056.8</v>
+        <v>45392.74</v>
       </c>
     </row>
     <row r="212">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1131.27</v>
+        <v>1165.57</v>
       </c>
     </row>
     <row r="213">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>31821.93</v>
+        <v>32767.77</v>
       </c>
     </row>
     <row r="214">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>34729.85</v>
+        <v>35762.13</v>
       </c>
     </row>
     <row r="215">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>29414.6</v>
+        <v>30288.89</v>
       </c>
     </row>
     <row r="216">
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>56563.28</v>
+        <v>58244.51</v>
       </c>
     </row>
     <row r="217">
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>7461.23</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="218">
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1488.57</v>
+        <v>1532.82</v>
       </c>
     </row>
     <row r="219">
@@ -13822,7 +13822,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>61463.36</v>
+        <v>63290.23</v>
       </c>
     </row>
     <row r="220">
@@ -13883,7 +13883,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>12443.92</v>
+        <v>12813.79</v>
       </c>
     </row>
     <row r="221">
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>49909.82</v>
+        <v>51393.29</v>
       </c>
     </row>
     <row r="222">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>5652.72</v>
+        <v>5820.74</v>
       </c>
     </row>
     <row r="223">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3489.95</v>
+        <v>3593.69</v>
       </c>
     </row>
     <row r="224">
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>20419.34</v>
+        <v>21026.27</v>
       </c>
     </row>
     <row r="225">
@@ -14188,7 +14188,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>535.2</v>
+        <v>551.11</v>
       </c>
     </row>
     <row r="226">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4134.67</v>
+        <v>4257.56</v>
       </c>
     </row>
     <row r="227">
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1541.07</v>
+        <v>1586.87</v>
       </c>
     </row>
     <row r="228">
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1433.54</v>
+        <v>1476.15</v>
       </c>
     </row>
     <row r="229">
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>73685.97</v>
+        <v>75876.13</v>
       </c>
     </row>
     <row r="230">
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>22625.31</v>
+        <v>23297.81</v>
       </c>
     </row>
     <row r="231">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>14228.74</v>
+        <v>14651.66</v>
       </c>
     </row>
     <row r="232">
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>21733.71</v>
+        <v>22379.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBCENTRO DE TELECOMUNICACIONES NAVALES (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7463,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8626,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8687,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8748,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8809,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8870,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8931,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8992,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9053,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9114,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9175,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9236,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9297,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9358,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9419,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9480,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9541,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9602,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9663,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9724,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9785,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9846,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9907,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9968,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10029,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10090,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10151,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10212,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10273,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10334,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10395,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10456,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10517,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10578,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10639,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10700,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10761,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10822,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10883,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10944,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11005,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11066,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11127,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11371,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11493,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11554,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11615,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11676,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11737,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11798,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11859,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11920,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11981,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12042,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12103,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12164,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12225,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12286,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12347,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12408,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12469,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12530,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12591,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12713,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12835,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13266,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13327,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13388,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13449,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13510,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13571,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13632,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13693,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13754,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13815,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13876,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13937,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13998,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14059,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14120,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14181,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14242,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14303,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14364,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14425,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14486,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14547,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14608,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
